--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL CONSUMIDOR</t>
+          <t>Servicio Nacional del Consumidor - SERNAC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1862,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1927,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1992,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2057,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2187,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2317,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2282,7 +2382,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2447,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2573,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2638,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2703,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2768,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
